--- a/SuppXLS/Scen_UC_DECRHEAT_MANHEAT_10_25.xlsx
+++ b/SuppXLS/Scen_UC_DECRHEAT_MANHEAT_10_25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D63E89-95DD-42BD-8E10-425B2ED33C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AA8778-E9ED-4680-8771-1EE2A587AF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
@@ -110,7 +110,7 @@
     <t>Minimum Decenteralized  Renewable heat penetration</t>
   </si>
   <si>
-    <t>UC_DECRHEAT_MANHEAT_10_50</t>
+    <t>UC_DECRHEAT_MANHEAT_10_25</t>
   </si>
 </sst>
 </file>
